--- a/03_Outputs/Penderisco_Sinifana/08_Educacion/educacion.xlsx
+++ b/03_Outputs/Penderisco_Sinifana/08_Educacion/educacion.xlsx
@@ -4372,13 +4372,13 @@
         <v>2021</v>
       </c>
       <c r="F121" s="7">
-        <v>0.872001779366615</v>
+        <v>0.793502501294906</v>
       </c>
       <c r="G121" s="9">
-        <v>0.0186323709192612</v>
+        <v>0.0629997086090639</v>
       </c>
       <c r="H121" s="11">
-        <v>0.111149943064852</v>
+        <v>0.0713185398011997</v>
       </c>
     </row>
     <row r="122">
@@ -4406,13 +4406,13 @@
         <v>2021</v>
       </c>
       <c r="F122" s="7">
-        <v>0.808399619674067</v>
+        <v>0.924418856993982</v>
       </c>
       <c r="G122" s="9">
-        <v>0.0340611041845194</v>
+        <v>0.0471531226376282</v>
       </c>
       <c r="H122" s="11">
-        <v>0.0537186135094694</v>
+        <v>0.0582136438740334</v>
       </c>
     </row>
     <row r="123">
